--- a/docs/qa/upload-templates/sales_orders_upload_template.xlsx
+++ b/docs/qa/upload-templates/sales_orders_upload_template.xlsx
@@ -148,20 +148,45 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
+        <t>YYYY-MM-DD</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
         <t>Numeric &gt;= 0</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>YYYY-MM-DD</t>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>YYYY-MM-DD</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>YYYY-MM-DD</t>
       </text>
@@ -459,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,32 +495,57 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>line_number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>customer_code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>product_code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>uom</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>order_date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>requested_delivery</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>warehouse</t>
         </is>
       </c>
     </row>
@@ -505,32 +555,53 @@
           <t>SO-2026-0289</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>CUST-SEC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>FG-DT250</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>92000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>WH-FG</t>
         </is>
       </c>
     </row>
@@ -540,32 +611,53 @@
           <t>SO-2026-0290</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>CUST-EE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FG-DT100</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>WH-FG</t>
         </is>
       </c>
     </row>
@@ -575,32 +667,53 @@
           <t>SO-2026-0291</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>CUST-DW</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>FG-DT100</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>52000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>draft</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>WH-FG</t>
         </is>
       </c>
     </row>
